--- a/projects/gpu-market/二手显卡行情.xlsx
+++ b/projects/gpu-market/二手显卡行情.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raopa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5347728-5800-4A38-8B5E-7D7EE2F494BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BE8356-AD54-4ED2-A0DF-2D25C14FDE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{663AC9E3-79A3-44FB-9AEC-B1684B123D3B}"/>
+    <workbookView xWindow="7220" yWindow="3980" windowWidth="28800" windowHeight="15370" activeTab="5" xr2:uid="{663AC9E3-79A3-44FB-9AEC-B1684B123D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="202512" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="202602" sheetId="2" r:id="rId3"/>
     <sheet name="202603" sheetId="1" r:id="rId4"/>
     <sheet name="202604" sheetId="5" r:id="rId5"/>
+    <sheet name="202605" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="166">
   <si>
     <t>显卡型号</t>
   </si>
@@ -550,15 +551,18 @@
       <t>G</t>
     </r>
   </si>
+  <si>
+    <t>5月价格</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="180" formatCode="0_ "/>
-    <numFmt numFmtId="181" formatCode="0.0%"/>
-    <numFmt numFmtId="182" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -730,7 +734,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -745,13 +749,13 @@
     <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -766,13 +770,13 @@
     <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -793,13 +797,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -817,13 +821,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -844,13 +848,13 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -883,10 +887,10 @@
     <xf numFmtId="17" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -28475,4 +28479,4664 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6DC5D4F-B590-48F7-B45A-27DC5061040F}">
+  <dimension ref="A1:L122"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.9140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="17.5">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="17.5">
+      <c r="A2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="8">
+        <v>45664</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="7">
+        <v>47331</v>
+      </c>
+      <c r="E2" s="7">
+        <v>570</v>
+      </c>
+      <c r="F2" s="9">
+        <v>26999</v>
+      </c>
+      <c r="G2" s="9">
+        <v>26300</v>
+      </c>
+      <c r="H2" s="9">
+        <v>-699</v>
+      </c>
+      <c r="I2" s="10">
+        <v>3.4753652984800598</v>
+      </c>
+      <c r="J2" s="11">
+        <v>1.79965779467681</v>
+      </c>
+      <c r="K2" s="11">
+        <v>83.036842105263204</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17.5">
+      <c r="A3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="8">
+        <v>45664</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="7">
+        <v>47489</v>
+      </c>
+      <c r="E3" s="7">
+        <v>570</v>
+      </c>
+      <c r="F3" s="9">
+        <v>23000</v>
+      </c>
+      <c r="G3" s="9">
+        <v>20794</v>
+      </c>
+      <c r="H3" s="9">
+        <v>-2206</v>
+      </c>
+      <c r="I3" s="10">
+        <v>3.4869667376459401</v>
+      </c>
+      <c r="J3" s="11">
+        <v>2.2837837837837802</v>
+      </c>
+      <c r="K3" s="11">
+        <v>83.314035087719304</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="17.5">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="8">
+        <v>44846</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="7">
+        <v>36538</v>
+      </c>
+      <c r="E4" s="7">
+        <v>450</v>
+      </c>
+      <c r="F4" s="9">
+        <v>16800</v>
+      </c>
+      <c r="G4" s="9">
+        <v>18100</v>
+      </c>
+      <c r="H4" s="9">
+        <v>1300</v>
+      </c>
+      <c r="I4" s="10">
+        <v>2.6828695205228001</v>
+      </c>
+      <c r="J4" s="11">
+        <v>2.0186740331491699</v>
+      </c>
+      <c r="K4" s="11">
+        <v>81.1955555555556</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17.5">
+      <c r="A5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="8">
+        <v>45288</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7">
+        <v>34204</v>
+      </c>
+      <c r="E5" s="7">
+        <v>425</v>
+      </c>
+      <c r="F5" s="9">
+        <v>17000</v>
+      </c>
+      <c r="G5" s="9">
+        <v>16863</v>
+      </c>
+      <c r="H5" s="9">
+        <v>-137</v>
+      </c>
+      <c r="I5" s="10">
+        <v>2.5114912989206299</v>
+      </c>
+      <c r="J5" s="11">
+        <v>2.0283460831406002</v>
+      </c>
+      <c r="K5" s="11">
+        <v>80.48</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17.5">
+      <c r="A6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="8">
+        <v>45881</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7">
+        <v>46501</v>
+      </c>
+      <c r="E6" s="7">
+        <v>570</v>
+      </c>
+      <c r="F6" s="9">
+        <v>16150</v>
+      </c>
+      <c r="G6" s="9">
+        <v>16400</v>
+      </c>
+      <c r="H6" s="9">
+        <v>250</v>
+      </c>
+      <c r="I6" s="10">
+        <v>3.4144210294441599</v>
+      </c>
+      <c r="J6" s="11">
+        <v>2.83542682926829</v>
+      </c>
+      <c r="K6" s="11">
+        <v>81.580701754385998</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17.5">
+      <c r="A7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="8">
+        <v>45664</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="7">
+        <v>33071</v>
+      </c>
+      <c r="E7" s="7">
+        <v>360</v>
+      </c>
+      <c r="F7" s="9">
+        <v>8450</v>
+      </c>
+      <c r="G7" s="9">
+        <v>8574</v>
+      </c>
+      <c r="H7" s="9">
+        <v>124</v>
+      </c>
+      <c r="I7" s="10">
+        <v>2.4282987003451102</v>
+      </c>
+      <c r="J7" s="11">
+        <v>3.8571261954746898</v>
+      </c>
+      <c r="K7" s="11">
+        <v>91.863888888888894</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="17.5">
+      <c r="A8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="8">
+        <v>45321</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="7">
+        <v>28469</v>
+      </c>
+      <c r="E8" s="7">
+        <v>320</v>
+      </c>
+      <c r="F8" s="9">
+        <v>6550</v>
+      </c>
+      <c r="G8" s="9">
+        <v>6500</v>
+      </c>
+      <c r="H8" s="9">
+        <v>-50</v>
+      </c>
+      <c r="I8" s="10">
+        <v>2.0903884279315701</v>
+      </c>
+      <c r="J8" s="11">
+        <v>4.3798461538461497</v>
+      </c>
+      <c r="K8" s="11">
+        <v>88.965625000000003</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17.5">
+      <c r="A9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8">
+        <v>44649</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="7">
+        <v>22038</v>
+      </c>
+      <c r="E9" s="7">
+        <v>450</v>
+      </c>
+      <c r="F9" s="9">
+        <v>6400</v>
+      </c>
+      <c r="G9" s="9">
+        <v>6500</v>
+      </c>
+      <c r="H9" s="9">
+        <v>100</v>
+      </c>
+      <c r="I9" s="10">
+        <v>1.61818048314854</v>
+      </c>
+      <c r="J9" s="11">
+        <v>3.39046153846154</v>
+      </c>
+      <c r="K9" s="11">
+        <v>48.973333333333301</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17.5">
+      <c r="A10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8">
+        <v>45664</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="7">
+        <v>27686</v>
+      </c>
+      <c r="E10" s="7">
+        <v>300</v>
+      </c>
+      <c r="F10" s="9">
+        <v>6394</v>
+      </c>
+      <c r="G10" s="9">
+        <v>6500</v>
+      </c>
+      <c r="H10" s="9">
+        <v>106</v>
+      </c>
+      <c r="I10" s="10">
+        <v>2.0328952199133599</v>
+      </c>
+      <c r="J10" s="11">
+        <v>4.2593846153846204</v>
+      </c>
+      <c r="K10" s="11">
+        <v>92.286666666666704</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.5">
+      <c r="A11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="8">
+        <v>44881</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="7">
+        <v>28221</v>
+      </c>
+      <c r="E11" s="7">
+        <v>320</v>
+      </c>
+      <c r="F11" s="9">
+        <v>6100</v>
+      </c>
+      <c r="G11" s="9">
+        <v>6100</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="10">
+        <v>2.0721785740509602</v>
+      </c>
+      <c r="J11" s="11">
+        <v>4.62639344262295</v>
+      </c>
+      <c r="K11" s="11">
+        <v>88.190624999999997</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17.5">
+      <c r="A12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="8">
+        <v>44098</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="7">
+        <v>19874</v>
+      </c>
+      <c r="E12" s="7">
+        <v>350</v>
+      </c>
+      <c r="F12" s="9">
+        <v>5150</v>
+      </c>
+      <c r="G12" s="9">
+        <v>5299</v>
+      </c>
+      <c r="H12" s="9">
+        <v>149</v>
+      </c>
+      <c r="I12" s="10">
+        <v>1.4592848226742099</v>
+      </c>
+      <c r="J12" s="11">
+        <v>3.7505189658426099</v>
+      </c>
+      <c r="K12" s="11">
+        <v>56.782857142857097</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.5">
+      <c r="A13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="8">
+        <v>45314</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="7">
+        <v>24343</v>
+      </c>
+      <c r="E13" s="7">
+        <v>285</v>
+      </c>
+      <c r="F13" s="9">
+        <v>4850</v>
+      </c>
+      <c r="G13" s="9">
+        <v>4700</v>
+      </c>
+      <c r="H13" s="9">
+        <v>-150</v>
+      </c>
+      <c r="I13" s="10">
+        <v>1.78742932667597</v>
+      </c>
+      <c r="J13" s="11">
+        <v>5.1793617021276601</v>
+      </c>
+      <c r="K13" s="11">
+        <v>85.414035087719299</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17.5">
+      <c r="A14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="8">
+        <v>45664</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="7">
+        <v>22626</v>
+      </c>
+      <c r="E14" s="7">
+        <v>250</v>
+      </c>
+      <c r="F14" s="9">
+        <v>4460</v>
+      </c>
+      <c r="G14" s="9">
+        <v>4390</v>
+      </c>
+      <c r="H14" s="9">
+        <v>-70</v>
+      </c>
+      <c r="I14" s="10">
+        <v>1.6613554592848201</v>
+      </c>
+      <c r="J14" s="11">
+        <v>5.1539863325740303</v>
+      </c>
+      <c r="K14" s="11">
+        <v>90.504000000000005</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17.5">
+      <c r="A15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="8">
+        <v>45716</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="7">
+        <v>30210</v>
+      </c>
+      <c r="E15" s="7">
+        <v>304</v>
+      </c>
+      <c r="F15" s="9">
+        <v>4250</v>
+      </c>
+      <c r="G15" s="9">
+        <v>4195</v>
+      </c>
+      <c r="H15" s="9">
+        <v>-55</v>
+      </c>
+      <c r="I15" s="10">
+        <v>2.21822453924664</v>
+      </c>
+      <c r="J15" s="11">
+        <v>7.2014302741358804</v>
+      </c>
+      <c r="K15" s="11">
+        <v>99.375</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17.5">
+      <c r="A16" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="8">
+        <v>44908</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="7">
+        <v>30432</v>
+      </c>
+      <c r="E16" s="7">
+        <v>355</v>
+      </c>
+      <c r="F16" s="9">
+        <v>4300</v>
+      </c>
+      <c r="G16" s="9">
+        <v>4100</v>
+      </c>
+      <c r="H16" s="9">
+        <v>-200</v>
+      </c>
+      <c r="I16" s="10">
+        <v>2.2345252955429902</v>
+      </c>
+      <c r="J16" s="11">
+        <v>7.4224390243902398</v>
+      </c>
+      <c r="K16" s="11">
+        <v>85.723943661971802</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17.5">
+      <c r="A17" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="15">
+        <v>44931</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="14">
+        <v>22806</v>
+      </c>
+      <c r="E17" s="14">
+        <v>285</v>
+      </c>
+      <c r="F17" s="16">
+        <v>3908</v>
+      </c>
+      <c r="G17" s="16">
+        <v>3820</v>
+      </c>
+      <c r="H17" s="16">
+        <v>-88</v>
+      </c>
+      <c r="I17" s="17">
+        <v>1.6745722887143</v>
+      </c>
+      <c r="J17" s="18">
+        <v>5.9701570680628304</v>
+      </c>
+      <c r="K17" s="18">
+        <v>80.021052631578996</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17.5">
+      <c r="A18" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="15">
+        <v>45716</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="14">
+        <v>27002</v>
+      </c>
+      <c r="E18" s="14">
+        <v>220</v>
+      </c>
+      <c r="F18" s="16">
+        <v>3755</v>
+      </c>
+      <c r="G18" s="16">
+        <v>3650</v>
+      </c>
+      <c r="H18" s="16">
+        <v>-105</v>
+      </c>
+      <c r="I18" s="17">
+        <v>1.9826712680813601</v>
+      </c>
+      <c r="J18" s="18">
+        <v>7.3978082191780796</v>
+      </c>
+      <c r="K18" s="18">
+        <v>122.736363636364</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17.5">
+      <c r="A19" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="15">
+        <v>45307</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="14">
+        <v>21076</v>
+      </c>
+      <c r="E19" s="14">
+        <v>220</v>
+      </c>
+      <c r="F19" s="16">
+        <v>3516</v>
+      </c>
+      <c r="G19" s="16">
+        <v>3450</v>
+      </c>
+      <c r="H19" s="16">
+        <v>-66</v>
+      </c>
+      <c r="I19" s="17">
+        <v>1.54754387253102</v>
+      </c>
+      <c r="J19" s="18">
+        <v>6.1089855072463797</v>
+      </c>
+      <c r="K19" s="18">
+        <v>95.8</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="17.5">
+      <c r="A20" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="15">
+        <v>45763</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="14">
+        <v>15954</v>
+      </c>
+      <c r="E20" s="14">
+        <v>180</v>
+      </c>
+      <c r="F20" s="16">
+        <v>3400</v>
+      </c>
+      <c r="G20" s="16">
+        <v>3300</v>
+      </c>
+      <c r="H20" s="16">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="17">
+        <v>1.1714516484323401</v>
+      </c>
+      <c r="J20" s="18">
+        <v>4.8345454545454496</v>
+      </c>
+      <c r="K20" s="18">
+        <v>88.633333333333297</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="17.5">
+      <c r="A21" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="15">
+        <v>44908</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="14">
+        <v>26586</v>
+      </c>
+      <c r="E21" s="14">
+        <v>315</v>
+      </c>
+      <c r="F21" s="16">
+        <v>3350</v>
+      </c>
+      <c r="G21" s="16">
+        <v>3200</v>
+      </c>
+      <c r="H21" s="16">
+        <v>-150</v>
+      </c>
+      <c r="I21" s="17">
+        <v>1.95212570673324</v>
+      </c>
+      <c r="J21" s="18">
+        <v>8.3081250000000004</v>
+      </c>
+      <c r="K21" s="18">
+        <v>84.4</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17.5">
+      <c r="A22" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="15">
+        <v>45785</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="14">
+        <v>22748</v>
+      </c>
+      <c r="E22" s="14">
+        <v>220</v>
+      </c>
+      <c r="F22" s="16">
+        <v>3100</v>
+      </c>
+      <c r="G22" s="16">
+        <v>3050</v>
+      </c>
+      <c r="H22" s="16">
+        <v>-50</v>
+      </c>
+      <c r="I22" s="17">
+        <v>1.6703135325648</v>
+      </c>
+      <c r="J22" s="18">
+        <v>7.4583606557376996</v>
+      </c>
+      <c r="K22" s="18">
+        <v>103.4</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17.5">
+      <c r="A23" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="8">
+        <v>45029</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="7">
+        <v>17866</v>
+      </c>
+      <c r="E23" s="7">
+        <v>200</v>
+      </c>
+      <c r="F23" s="9">
+        <v>3086</v>
+      </c>
+      <c r="G23" s="9">
+        <v>2950</v>
+      </c>
+      <c r="H23" s="9">
+        <v>-136</v>
+      </c>
+      <c r="I23" s="10">
+        <v>1.3118437477054099</v>
+      </c>
+      <c r="J23" s="11">
+        <v>6.0562711864406804</v>
+      </c>
+      <c r="K23" s="11">
+        <v>89.33</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="17.5">
+      <c r="A24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="8">
+        <v>45125</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="7">
+        <v>13509</v>
+      </c>
+      <c r="E24" s="7">
+        <v>150</v>
+      </c>
+      <c r="F24" s="9">
+        <v>2800</v>
+      </c>
+      <c r="G24" s="9">
+        <v>2799</v>
+      </c>
+      <c r="H24" s="9">
+        <v>-1</v>
+      </c>
+      <c r="I24" s="10">
+        <v>0.991923048681988</v>
+      </c>
+      <c r="J24" s="11">
+        <v>4.8263665594855301</v>
+      </c>
+      <c r="K24" s="11">
+        <v>90.06</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="17.5">
+      <c r="A25" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="8">
+        <v>44350</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="7">
+        <v>19744</v>
+      </c>
+      <c r="E25" s="7">
+        <v>350</v>
+      </c>
+      <c r="F25" s="9">
+        <v>2760</v>
+      </c>
+      <c r="G25" s="9">
+        <v>2715</v>
+      </c>
+      <c r="H25" s="9">
+        <v>-45</v>
+      </c>
+      <c r="I25" s="10">
+        <v>1.4497393347529199</v>
+      </c>
+      <c r="J25" s="11">
+        <v>7.27219152854512</v>
+      </c>
+      <c r="K25" s="11">
+        <v>56.411428571428601</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="17.5">
+      <c r="A26" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="8">
+        <v>45134</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="7">
+        <v>22039</v>
+      </c>
+      <c r="E26" s="7">
+        <v>260</v>
+      </c>
+      <c r="F26" s="9">
+        <v>2750</v>
+      </c>
+      <c r="G26" s="9">
+        <v>2699</v>
+      </c>
+      <c r="H26" s="9">
+        <v>-51</v>
+      </c>
+      <c r="I26" s="10">
+        <v>1.6182539099787101</v>
+      </c>
+      <c r="J26" s="11">
+        <v>8.1656168951463499</v>
+      </c>
+      <c r="K26" s="11">
+        <v>84.765384615384605</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="17.5">
+      <c r="A27" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="8">
+        <v>45763</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="7">
+        <v>15889</v>
+      </c>
+      <c r="E27" s="7">
+        <v>180</v>
+      </c>
+      <c r="F27" s="9">
+        <v>2599</v>
+      </c>
+      <c r="G27" s="9">
+        <v>2550</v>
+      </c>
+      <c r="H27" s="9">
+        <v>-49</v>
+      </c>
+      <c r="I27" s="10">
+        <v>1.1666789044716901</v>
+      </c>
+      <c r="J27" s="11">
+        <v>6.2309803921568596</v>
+      </c>
+      <c r="K27" s="11">
+        <v>88.272222222222197</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17.5">
+      <c r="A28" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="23">
+        <v>44588</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="24">
+        <v>18760</v>
+      </c>
+      <c r="E28" s="24">
+        <v>350</v>
+      </c>
+      <c r="F28" s="25">
+        <v>2399</v>
+      </c>
+      <c r="G28" s="25">
+        <v>2450</v>
+      </c>
+      <c r="H28" s="25">
+        <v>51</v>
+      </c>
+      <c r="I28" s="26">
+        <v>1.3774873338717999</v>
+      </c>
+      <c r="J28" s="27">
+        <v>7.6571428571428601</v>
+      </c>
+      <c r="K28" s="27">
+        <v>53.6</v>
+      </c>
+      <c r="L28" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="17.5">
+      <c r="A29" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="23">
+        <v>45796</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="24">
+        <v>13619</v>
+      </c>
+      <c r="E29" s="24">
+        <v>145</v>
+      </c>
+      <c r="F29" s="25">
+        <v>2399</v>
+      </c>
+      <c r="G29" s="25">
+        <v>2399</v>
+      </c>
+      <c r="H29" s="25">
+        <v>0</v>
+      </c>
+      <c r="I29" s="26">
+        <v>1</v>
+      </c>
+      <c r="J29" s="27">
+        <v>5.6769487286369298</v>
+      </c>
+      <c r="K29" s="27">
+        <v>93.924137931034494</v>
+      </c>
+      <c r="L29" s="28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="17.5">
+      <c r="A30" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="23">
+        <v>45175</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="24">
+        <v>20024</v>
+      </c>
+      <c r="E30" s="24">
+        <v>263</v>
+      </c>
+      <c r="F30" s="25">
+        <v>2450</v>
+      </c>
+      <c r="G30" s="25">
+        <v>2380</v>
+      </c>
+      <c r="H30" s="25">
+        <v>-70</v>
+      </c>
+      <c r="I30" s="26">
+        <v>1.4702988471987699</v>
+      </c>
+      <c r="J30" s="27">
+        <v>8.4134453781512608</v>
+      </c>
+      <c r="K30" s="27">
+        <v>76.136882129277595</v>
+      </c>
+      <c r="L30" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="17.5">
+      <c r="A31" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="23">
+        <v>45798</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="24">
+        <v>16553</v>
+      </c>
+      <c r="E31" s="24">
+        <v>160</v>
+      </c>
+      <c r="F31" s="25">
+        <v>2350</v>
+      </c>
+      <c r="G31" s="25">
+        <v>2299</v>
+      </c>
+      <c r="H31" s="25">
+        <v>-51</v>
+      </c>
+      <c r="I31" s="26">
+        <v>1.21543431970042</v>
+      </c>
+      <c r="J31" s="27">
+        <v>7.2000869943453703</v>
+      </c>
+      <c r="K31" s="27">
+        <v>103.45625</v>
+      </c>
+      <c r="L31" s="28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="17.5">
+      <c r="A32" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="23">
+        <v>44691</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="24">
+        <v>21434</v>
+      </c>
+      <c r="E32" s="24">
+        <v>335</v>
+      </c>
+      <c r="F32" s="25">
+        <v>2325</v>
+      </c>
+      <c r="G32" s="25">
+        <v>2295</v>
+      </c>
+      <c r="H32" s="25">
+        <v>-30</v>
+      </c>
+      <c r="I32" s="26">
+        <v>1.57383067772964</v>
+      </c>
+      <c r="J32" s="27">
+        <v>9.33943355119826</v>
+      </c>
+      <c r="K32" s="27">
+        <v>63.982089552238797</v>
+      </c>
+      <c r="L32" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="17.5">
+      <c r="A33" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="31">
+        <v>45070</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="32">
+        <v>13509</v>
+      </c>
+      <c r="E33" s="32">
+        <v>150</v>
+      </c>
+      <c r="F33" s="33">
+        <v>2055</v>
+      </c>
+      <c r="G33" s="33">
+        <v>1950</v>
+      </c>
+      <c r="H33" s="33">
+        <v>-105</v>
+      </c>
+      <c r="I33" s="34">
+        <v>0.991923048681988</v>
+      </c>
+      <c r="J33" s="35">
+        <v>6.9276923076923103</v>
+      </c>
+      <c r="K33" s="35">
+        <v>90.06</v>
+      </c>
+      <c r="L33" s="36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="17.5">
+      <c r="A34" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="31">
+        <v>44091</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="32">
+        <v>17706</v>
+      </c>
+      <c r="E34" s="32">
+        <v>320</v>
+      </c>
+      <c r="F34" s="33">
+        <v>2023</v>
+      </c>
+      <c r="G34" s="33">
+        <v>1950</v>
+      </c>
+      <c r="H34" s="33">
+        <v>-73</v>
+      </c>
+      <c r="I34" s="34">
+        <v>1.3000954548792101</v>
+      </c>
+      <c r="J34" s="35">
+        <v>9.08</v>
+      </c>
+      <c r="K34" s="35">
+        <v>55.331249999999997</v>
+      </c>
+      <c r="L34" s="36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="17.5">
+      <c r="A35" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="31">
+        <v>44173</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="32">
+        <v>20912</v>
+      </c>
+      <c r="E35" s="32">
+        <v>300</v>
+      </c>
+      <c r="F35" s="33">
+        <v>1998</v>
+      </c>
+      <c r="G35" s="33">
+        <v>1931</v>
+      </c>
+      <c r="H35" s="33">
+        <v>-67</v>
+      </c>
+      <c r="I35" s="34">
+        <v>1.53550187238417</v>
+      </c>
+      <c r="J35" s="35">
+        <v>10.829621957535</v>
+      </c>
+      <c r="K35" s="35">
+        <v>69.706666666666706</v>
+      </c>
+      <c r="L35" s="36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="17.5">
+      <c r="A36" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="31">
+        <v>45175</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="32">
+        <v>17060</v>
+      </c>
+      <c r="E36" s="32">
+        <v>245</v>
+      </c>
+      <c r="F36" s="33">
+        <v>1900</v>
+      </c>
+      <c r="G36" s="33">
+        <v>1850</v>
+      </c>
+      <c r="H36" s="33">
+        <v>-50</v>
+      </c>
+      <c r="I36" s="34">
+        <v>1.25266172259344</v>
+      </c>
+      <c r="J36" s="35">
+        <v>9.2216216216216207</v>
+      </c>
+      <c r="K36" s="35">
+        <v>69.632653061224502</v>
+      </c>
+      <c r="L36" s="36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="17.5">
+      <c r="A37" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="31">
+        <v>45813</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="32">
+        <v>16275</v>
+      </c>
+      <c r="E37" s="32">
+        <v>160</v>
+      </c>
+      <c r="F37" s="33">
+        <v>1925</v>
+      </c>
+      <c r="G37" s="33">
+        <v>1800</v>
+      </c>
+      <c r="H37" s="33">
+        <v>-125</v>
+      </c>
+      <c r="I37" s="34">
+        <v>1.1950216609149</v>
+      </c>
+      <c r="J37" s="35">
+        <v>9.0416666666666696</v>
+      </c>
+      <c r="K37" s="35">
+        <v>101.71875</v>
+      </c>
+      <c r="L37" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="17.5">
+      <c r="A38" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="31">
+        <v>45106</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="32">
+        <v>10627</v>
+      </c>
+      <c r="E38" s="32">
+        <v>115</v>
+      </c>
+      <c r="F38" s="33">
+        <v>1850</v>
+      </c>
+      <c r="G38" s="33">
+        <v>1729</v>
+      </c>
+      <c r="H38" s="33">
+        <v>-121</v>
+      </c>
+      <c r="I38" s="34">
+        <v>0.78030692415008396</v>
+      </c>
+      <c r="J38" s="35">
+        <v>6.1463273568536696</v>
+      </c>
+      <c r="K38" s="35">
+        <v>92.408695652173904</v>
+      </c>
+      <c r="L38" s="36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="17.5">
+      <c r="A39" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="31">
+        <v>44357</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="32">
+        <v>14952</v>
+      </c>
+      <c r="E39" s="32">
+        <v>290</v>
+      </c>
+      <c r="F39" s="33">
+        <v>1700</v>
+      </c>
+      <c r="G39" s="33">
+        <v>1680</v>
+      </c>
+      <c r="H39" s="33">
+        <v>-20</v>
+      </c>
+      <c r="I39" s="34">
+        <v>1.0978779646082699</v>
+      </c>
+      <c r="J39" s="35">
+        <v>8.9</v>
+      </c>
+      <c r="K39" s="35">
+        <v>51.5586206896552</v>
+      </c>
+      <c r="L39" s="36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="17.5">
+      <c r="A40" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="31">
+        <v>45832</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" s="32">
+        <v>10259</v>
+      </c>
+      <c r="E40" s="32">
+        <v>130</v>
+      </c>
+      <c r="F40" s="33">
+        <v>1719</v>
+      </c>
+      <c r="G40" s="33">
+        <v>1670</v>
+      </c>
+      <c r="H40" s="33">
+        <v>-49</v>
+      </c>
+      <c r="I40" s="34">
+        <v>0.753285850649827</v>
+      </c>
+      <c r="J40" s="35">
+        <v>6.1431137724550897</v>
+      </c>
+      <c r="K40" s="35">
+        <v>78.915384615384596</v>
+      </c>
+      <c r="L40" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="17.5">
+      <c r="A41" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="31">
+        <v>44153</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="32">
+        <v>19420</v>
+      </c>
+      <c r="E41" s="32">
+        <v>300</v>
+      </c>
+      <c r="F41" s="33">
+        <v>1718</v>
+      </c>
+      <c r="G41" s="33">
+        <v>1666</v>
+      </c>
+      <c r="H41" s="33">
+        <v>-52</v>
+      </c>
+      <c r="I41" s="34">
+        <v>1.4259490417798699</v>
+      </c>
+      <c r="J41" s="35">
+        <v>11.656662665065999</v>
+      </c>
+      <c r="K41" s="35">
+        <v>64.733333333333306</v>
+      </c>
+      <c r="L41" s="36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="17.5">
+      <c r="A42" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="31">
+        <v>45629</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="32">
+        <v>14923</v>
+      </c>
+      <c r="E42" s="32">
+        <v>190</v>
+      </c>
+      <c r="F42" s="33">
+        <v>1650</v>
+      </c>
+      <c r="G42" s="33">
+        <v>1649</v>
+      </c>
+      <c r="H42" s="33">
+        <v>-1</v>
+      </c>
+      <c r="I42" s="34">
+        <v>1.0957485865335199</v>
+      </c>
+      <c r="J42" s="35">
+        <v>9.0497271073377803</v>
+      </c>
+      <c r="K42" s="35">
+        <v>78.542105263157893</v>
+      </c>
+      <c r="L42" s="36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="17.5">
+      <c r="A43" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="31">
+        <v>44153</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" s="32">
+        <v>16313</v>
+      </c>
+      <c r="E43" s="32">
+        <v>250</v>
+      </c>
+      <c r="F43" s="33">
+        <v>1500</v>
+      </c>
+      <c r="G43" s="33">
+        <v>1520</v>
+      </c>
+      <c r="H43" s="33">
+        <v>20</v>
+      </c>
+      <c r="I43" s="34">
+        <v>1.19781188046112</v>
+      </c>
+      <c r="J43" s="35">
+        <v>10.7322368421053</v>
+      </c>
+      <c r="K43" s="35">
+        <v>65.251999999999995</v>
+      </c>
+      <c r="L43" s="36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="17.5">
+      <c r="A44" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="40">
+        <v>44861</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="41">
+        <v>12214</v>
+      </c>
+      <c r="E44" s="41">
+        <v>200</v>
+      </c>
+      <c r="F44" s="42">
+        <v>1580</v>
+      </c>
+      <c r="G44" s="42">
+        <v>1499</v>
+      </c>
+      <c r="H44" s="42">
+        <v>-81</v>
+      </c>
+      <c r="I44" s="43">
+        <v>0.89683530361994301</v>
+      </c>
+      <c r="J44" s="44">
+        <v>8.1480987324883305</v>
+      </c>
+      <c r="K44" s="44">
+        <v>61.07</v>
+      </c>
+      <c r="L44" s="45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="17.5">
+      <c r="A45" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="40">
+        <v>44133</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="41">
+        <v>13640</v>
+      </c>
+      <c r="E45" s="41">
+        <v>220</v>
+      </c>
+      <c r="F45" s="42">
+        <v>1500</v>
+      </c>
+      <c r="G45" s="42">
+        <v>1467</v>
+      </c>
+      <c r="H45" s="42">
+        <v>-33</v>
+      </c>
+      <c r="I45" s="43">
+        <v>1.0015419634334399</v>
+      </c>
+      <c r="J45" s="44">
+        <v>9.2978868438991107</v>
+      </c>
+      <c r="K45" s="44">
+        <v>62</v>
+      </c>
+      <c r="L45" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="17.5">
+      <c r="A46" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" s="40">
+        <v>44208</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="41">
+        <v>8753</v>
+      </c>
+      <c r="E46" s="41">
+        <v>170</v>
+      </c>
+      <c r="F46" s="42">
+        <v>1500</v>
+      </c>
+      <c r="G46" s="42">
+        <v>1450</v>
+      </c>
+      <c r="H46" s="42">
+        <v>-50</v>
+      </c>
+      <c r="I46" s="43">
+        <v>0.64270504442323195</v>
+      </c>
+      <c r="J46" s="44">
+        <v>6.0365517241379303</v>
+      </c>
+      <c r="K46" s="44">
+        <v>51.488235294117601</v>
+      </c>
+      <c r="L46" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="17.5">
+      <c r="A47" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="40">
+        <v>45217</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="41">
+        <v>12623</v>
+      </c>
+      <c r="E47" s="41">
+        <v>230</v>
+      </c>
+      <c r="F47" s="42">
+        <v>1515</v>
+      </c>
+      <c r="G47" s="42">
+        <v>1420</v>
+      </c>
+      <c r="H47" s="42">
+        <v>-95</v>
+      </c>
+      <c r="I47" s="43">
+        <v>0.92686687715691296</v>
+      </c>
+      <c r="J47" s="44">
+        <v>8.8894366197183103</v>
+      </c>
+      <c r="K47" s="44">
+        <v>54.882608695652202</v>
+      </c>
+      <c r="L47" s="45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="17.5">
+      <c r="A48" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="40">
+        <v>44691</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="41">
+        <v>13498</v>
+      </c>
+      <c r="E48" s="41">
+        <v>250</v>
+      </c>
+      <c r="F48" s="42">
+        <v>1450</v>
+      </c>
+      <c r="G48" s="42">
+        <v>1400</v>
+      </c>
+      <c r="H48" s="42">
+        <v>-50</v>
+      </c>
+      <c r="I48" s="43">
+        <v>0.99111535355018698</v>
+      </c>
+      <c r="J48" s="44">
+        <v>9.6414285714285697</v>
+      </c>
+      <c r="K48" s="44">
+        <v>53.991999999999997</v>
+      </c>
+      <c r="L48" s="45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="17.5">
+      <c r="A49" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="40">
+        <v>44167</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" s="41">
+        <v>11649</v>
+      </c>
+      <c r="E49" s="41">
+        <v>200</v>
+      </c>
+      <c r="F49" s="42">
+        <v>1450</v>
+      </c>
+      <c r="G49" s="42">
+        <v>1400</v>
+      </c>
+      <c r="H49" s="42">
+        <v>-50</v>
+      </c>
+      <c r="I49" s="43">
+        <v>0.85534914457742905</v>
+      </c>
+      <c r="J49" s="44">
+        <v>8.3207142857142795</v>
+      </c>
+      <c r="K49" s="44">
+        <v>58.244999999999997</v>
+      </c>
+      <c r="L49" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="17.5">
+      <c r="A50" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="40">
+        <v>44861</v>
+      </c>
+      <c r="C50" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50" s="41">
+        <v>7373</v>
+      </c>
+      <c r="E50" s="41">
+        <v>170</v>
+      </c>
+      <c r="F50" s="42">
+        <v>1450</v>
+      </c>
+      <c r="G50" s="42">
+        <v>1400</v>
+      </c>
+      <c r="H50" s="42">
+        <v>-50</v>
+      </c>
+      <c r="I50" s="43">
+        <v>0.54137601879726804</v>
+      </c>
+      <c r="J50" s="44">
+        <v>5.2664285714285697</v>
+      </c>
+      <c r="K50" s="44">
+        <v>43.3705882352941</v>
+      </c>
+      <c r="L50" s="45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="17.5">
+      <c r="A51" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="40">
+        <v>45673</v>
+      </c>
+      <c r="C51" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="41">
+        <v>12610</v>
+      </c>
+      <c r="E51" s="41">
+        <v>180</v>
+      </c>
+      <c r="F51" s="42">
+        <v>1350</v>
+      </c>
+      <c r="G51" s="42">
+        <v>1334</v>
+      </c>
+      <c r="H51" s="42">
+        <v>-16</v>
+      </c>
+      <c r="I51" s="43">
+        <v>0.92591232836478499</v>
+      </c>
+      <c r="J51" s="44">
+        <v>9.4527736131934006</v>
+      </c>
+      <c r="K51" s="44">
+        <v>70.0555555555556</v>
+      </c>
+      <c r="L51" s="45" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="17.5">
+      <c r="A52" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" s="40">
+        <v>43333</v>
+      </c>
+      <c r="C52" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" s="41">
+        <v>14617</v>
+      </c>
+      <c r="E52" s="41">
+        <v>260</v>
+      </c>
+      <c r="F52" s="42">
+        <v>1385</v>
+      </c>
+      <c r="G52" s="42">
+        <v>1313</v>
+      </c>
+      <c r="H52" s="42">
+        <v>-72</v>
+      </c>
+      <c r="I52" s="43">
+        <v>1.07327997650341</v>
+      </c>
+      <c r="J52" s="44">
+        <v>11.132520944402099</v>
+      </c>
+      <c r="K52" s="44">
+        <v>56.219230769230798</v>
+      </c>
+      <c r="L52" s="45" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="17.5">
+      <c r="A53" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="15">
+        <v>44848</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" s="14">
+        <v>13610</v>
+      </c>
+      <c r="E53" s="14">
+        <v>225</v>
+      </c>
+      <c r="F53" s="16">
+        <v>1280</v>
+      </c>
+      <c r="G53" s="16">
+        <v>1299</v>
+      </c>
+      <c r="H53" s="16">
+        <v>19</v>
+      </c>
+      <c r="I53" s="17">
+        <v>0.99933915852852595</v>
+      </c>
+      <c r="J53" s="18">
+        <v>10.4772902232487</v>
+      </c>
+      <c r="K53" s="18">
+        <v>60.488888888888901</v>
+      </c>
+      <c r="L53" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="17.5">
+      <c r="A54" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="15">
+        <v>45695</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D54" s="14">
+        <v>11158</v>
+      </c>
+      <c r="E54" s="14">
+        <v>170</v>
+      </c>
+      <c r="F54" s="16">
+        <v>1318</v>
+      </c>
+      <c r="G54" s="16">
+        <v>1293</v>
+      </c>
+      <c r="H54" s="16">
+        <v>-25</v>
+      </c>
+      <c r="I54" s="17">
+        <v>0.81929657096703101</v>
+      </c>
+      <c r="J54" s="18">
+        <v>8.6295436968290797</v>
+      </c>
+      <c r="K54" s="18">
+        <v>65.635294117647106</v>
+      </c>
+      <c r="L54" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="17.5">
+      <c r="A55" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" s="15">
+        <v>45217</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" s="14">
+        <v>11152</v>
+      </c>
+      <c r="E55" s="14">
+        <v>175</v>
+      </c>
+      <c r="F55" s="16">
+        <v>1300</v>
+      </c>
+      <c r="G55" s="16">
+        <v>1260</v>
+      </c>
+      <c r="H55" s="16">
+        <v>-40</v>
+      </c>
+      <c r="I55" s="17">
+        <v>0.81885600998604902</v>
+      </c>
+      <c r="J55" s="18">
+        <v>8.8507936507936495</v>
+      </c>
+      <c r="K55" s="18">
+        <v>63.725714285714297</v>
+      </c>
+      <c r="L55" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="17.5">
+      <c r="A56" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="15">
+        <v>44273</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="14">
+        <v>12773</v>
+      </c>
+      <c r="E56" s="14">
+        <v>230</v>
+      </c>
+      <c r="F56" s="16">
+        <v>1230</v>
+      </c>
+      <c r="G56" s="16">
+        <v>1188</v>
+      </c>
+      <c r="H56" s="16">
+        <v>-42</v>
+      </c>
+      <c r="I56" s="17">
+        <v>0.93788090168147398</v>
+      </c>
+      <c r="J56" s="18">
+        <v>10.7516835016835</v>
+      </c>
+      <c r="K56" s="18">
+        <v>55.5347826086957</v>
+      </c>
+      <c r="L56" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="17.5">
+      <c r="A57" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="15">
+        <v>45071</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57" s="14">
+        <v>10973</v>
+      </c>
+      <c r="E57" s="14">
+        <v>165</v>
+      </c>
+      <c r="F57" s="16">
+        <v>1231</v>
+      </c>
+      <c r="G57" s="16">
+        <v>1180</v>
+      </c>
+      <c r="H57" s="16">
+        <v>-51</v>
+      </c>
+      <c r="I57" s="17">
+        <v>0.805712607386739</v>
+      </c>
+      <c r="J57" s="18">
+        <v>9.2991525423728802</v>
+      </c>
+      <c r="K57" s="18">
+        <v>66.5030303030303</v>
+      </c>
+      <c r="L57" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="17.5">
+      <c r="A58" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="15">
+        <v>43669</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" s="14">
+        <v>11558</v>
+      </c>
+      <c r="E58" s="14">
+        <v>250</v>
+      </c>
+      <c r="F58" s="16">
+        <v>1199</v>
+      </c>
+      <c r="G58" s="16">
+        <v>1150</v>
+      </c>
+      <c r="H58" s="16">
+        <v>-49</v>
+      </c>
+      <c r="I58" s="17">
+        <v>0.84866730303252802</v>
+      </c>
+      <c r="J58" s="18">
+        <v>10.050434782608701</v>
+      </c>
+      <c r="K58" s="18">
+        <v>46.231999999999999</v>
+      </c>
+      <c r="L58" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="17.5">
+      <c r="A59" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" s="15">
+        <v>44691</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" s="14">
+        <v>9910</v>
+      </c>
+      <c r="E59" s="14">
+        <v>180</v>
+      </c>
+      <c r="F59" s="16">
+        <v>1100</v>
+      </c>
+      <c r="G59" s="16">
+        <v>1068</v>
+      </c>
+      <c r="H59" s="16">
+        <v>-32</v>
+      </c>
+      <c r="I59" s="17">
+        <v>0.72765988692268202</v>
+      </c>
+      <c r="J59" s="18">
+        <v>9.2790262172284592</v>
+      </c>
+      <c r="K59" s="18">
+        <v>55.0555555555556</v>
+      </c>
+      <c r="L59" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="17.5">
+      <c r="A60" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="B60" s="15">
+        <v>44848</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="14">
+        <v>13610</v>
+      </c>
+      <c r="E60" s="14">
+        <v>225</v>
+      </c>
+      <c r="F60" s="16">
+        <v>1150</v>
+      </c>
+      <c r="G60" s="16">
+        <v>1050</v>
+      </c>
+      <c r="H60" s="16">
+        <v>-100</v>
+      </c>
+      <c r="I60" s="17">
+        <v>0.99933915852852595</v>
+      </c>
+      <c r="J60" s="18">
+        <v>12.961904761904799</v>
+      </c>
+      <c r="K60" s="18">
+        <v>60.488888888888901</v>
+      </c>
+      <c r="L60" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="17.5">
+      <c r="A61" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B61" s="15">
+        <v>44537</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="14">
+        <v>8015</v>
+      </c>
+      <c r="E61" s="14">
+        <v>185</v>
+      </c>
+      <c r="F61" s="16">
+        <v>1055</v>
+      </c>
+      <c r="G61" s="16">
+        <v>1028</v>
+      </c>
+      <c r="H61" s="16">
+        <v>-27</v>
+      </c>
+      <c r="I61" s="17">
+        <v>0.58851604376239097</v>
+      </c>
+      <c r="J61" s="18">
+        <v>7.79669260700389</v>
+      </c>
+      <c r="K61" s="18">
+        <v>43.324324324324301</v>
+      </c>
+      <c r="L61" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="17.5">
+      <c r="A62" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B62" s="15">
+        <v>44588</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" s="14">
+        <v>6239</v>
+      </c>
+      <c r="E62" s="14">
+        <v>130</v>
+      </c>
+      <c r="F62" s="16">
+        <v>1030</v>
+      </c>
+      <c r="G62" s="16">
+        <v>1020</v>
+      </c>
+      <c r="H62" s="16">
+        <v>-10</v>
+      </c>
+      <c r="I62" s="17">
+        <v>0.45810999339158498</v>
+      </c>
+      <c r="J62" s="18">
+        <v>6.1166666666666698</v>
+      </c>
+      <c r="K62" s="18">
+        <v>47.992307692307698</v>
+      </c>
+      <c r="L62" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="17.5">
+      <c r="A63" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="B63" s="15">
+        <v>43648</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="14">
+        <v>10101</v>
+      </c>
+      <c r="E63" s="14">
+        <v>215</v>
+      </c>
+      <c r="F63" s="16">
+        <v>1050</v>
+      </c>
+      <c r="G63" s="16">
+        <v>1012</v>
+      </c>
+      <c r="H63" s="16">
+        <v>-38</v>
+      </c>
+      <c r="I63" s="17">
+        <v>0.74168441148395603</v>
+      </c>
+      <c r="J63" s="18">
+        <v>9.9812252964426893</v>
+      </c>
+      <c r="K63" s="18">
+        <v>46.981395348837196</v>
+      </c>
+      <c r="L63" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="17.5">
+      <c r="A64" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="B64" s="15">
+        <v>43333</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64" s="14">
+        <v>10972</v>
+      </c>
+      <c r="E64" s="14">
+        <v>225</v>
+      </c>
+      <c r="F64" s="16">
+        <v>1088</v>
+      </c>
+      <c r="G64" s="16">
+        <v>1000</v>
+      </c>
+      <c r="H64" s="16">
+        <v>-88</v>
+      </c>
+      <c r="I64" s="17">
+        <v>0.80563918055657502</v>
+      </c>
+      <c r="J64" s="18">
+        <v>10.972</v>
+      </c>
+      <c r="K64" s="18">
+        <v>48.764444444444401</v>
+      </c>
+      <c r="L64" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="17.5">
+      <c r="A65" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D65" s="7">
+        <v>4848</v>
+      </c>
+      <c r="E65" s="7">
+        <v>70</v>
+      </c>
+      <c r="F65" s="9">
+        <v>1020</v>
+      </c>
+      <c r="G65" s="9">
+        <v>950</v>
+      </c>
+      <c r="H65" s="9">
+        <v>-70</v>
+      </c>
+      <c r="I65" s="10">
+        <v>0.35597327263382</v>
+      </c>
+      <c r="J65" s="11">
+        <v>5.1031578947368397</v>
+      </c>
+      <c r="K65" s="11">
+        <v>69.257142857142895</v>
+      </c>
+      <c r="L65" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="17.5">
+      <c r="A66" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" s="8">
+        <v>43648</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" s="7">
+        <v>8640</v>
+      </c>
+      <c r="E66" s="7">
+        <v>175</v>
+      </c>
+      <c r="F66" s="9">
+        <v>950</v>
+      </c>
+      <c r="G66" s="9">
+        <v>950</v>
+      </c>
+      <c r="H66" s="9">
+        <v>0</v>
+      </c>
+      <c r="I66" s="10">
+        <v>0.63440781261472901</v>
+      </c>
+      <c r="J66" s="11">
+        <v>9.0947368421052595</v>
+      </c>
+      <c r="K66" s="11">
+        <v>49.371428571428602</v>
+      </c>
+      <c r="L66" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="17.5">
+      <c r="A67" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B67" s="8">
+        <v>44419</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="7">
+        <v>9579</v>
+      </c>
+      <c r="E67" s="7">
+        <v>160</v>
+      </c>
+      <c r="F67" s="9">
+        <v>942</v>
+      </c>
+      <c r="G67" s="9">
+        <v>950</v>
+      </c>
+      <c r="H67" s="9">
+        <v>8</v>
+      </c>
+      <c r="I67" s="10">
+        <v>0.70335560613848302</v>
+      </c>
+      <c r="J67" s="11">
+        <v>10.0831578947368</v>
+      </c>
+      <c r="K67" s="11">
+        <v>59.868749999999999</v>
+      </c>
+      <c r="L67" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="17.5">
+      <c r="A68" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" s="8">
+        <v>43333</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" s="7">
+        <v>8879</v>
+      </c>
+      <c r="E68" s="7">
+        <v>185</v>
+      </c>
+      <c r="F68" s="9">
+        <v>930</v>
+      </c>
+      <c r="G68" s="9">
+        <v>935</v>
+      </c>
+      <c r="H68" s="9">
+        <v>5</v>
+      </c>
+      <c r="I68" s="10">
+        <v>0.65195682502386398</v>
+      </c>
+      <c r="J68" s="11">
+        <v>9.4962566844919802</v>
+      </c>
+      <c r="K68" s="11">
+        <v>47.994594594594602</v>
+      </c>
+      <c r="L68" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="17.5">
+      <c r="A69" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" s="8">
+        <v>44848</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" s="7">
+        <v>12473</v>
+      </c>
+      <c r="E69" s="7">
+        <v>225</v>
+      </c>
+      <c r="F69" s="9">
+        <v>900</v>
+      </c>
+      <c r="G69" s="9">
+        <v>915</v>
+      </c>
+      <c r="H69" s="9">
+        <v>15</v>
+      </c>
+      <c r="I69" s="10">
+        <v>0.91585285263235205</v>
+      </c>
+      <c r="J69" s="11">
+        <v>13.631693989071</v>
+      </c>
+      <c r="K69" s="11">
+        <v>55.435555555555602</v>
+      </c>
+      <c r="L69" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="17.5">
+      <c r="A70" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" s="8">
+        <v>44482</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" s="7">
+        <v>8086</v>
+      </c>
+      <c r="E70" s="7">
+        <v>132</v>
+      </c>
+      <c r="F70" s="9">
+        <v>911</v>
+      </c>
+      <c r="G70" s="9">
+        <v>900</v>
+      </c>
+      <c r="H70" s="9">
+        <v>-11</v>
+      </c>
+      <c r="I70" s="10">
+        <v>0.59372934870401695</v>
+      </c>
+      <c r="J70" s="11">
+        <v>8.9844444444444402</v>
+      </c>
+      <c r="K70" s="11">
+        <v>61.2575757575758</v>
+      </c>
+      <c r="L70" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="17.5">
+      <c r="A71" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B71" s="8">
+        <v>43482</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D71" s="7">
+        <v>7490</v>
+      </c>
+      <c r="E71" s="7">
+        <v>160</v>
+      </c>
+      <c r="F71" s="9">
+        <v>839</v>
+      </c>
+      <c r="G71" s="9">
+        <v>850</v>
+      </c>
+      <c r="H71" s="9">
+        <v>11</v>
+      </c>
+      <c r="I71" s="10">
+        <v>0.54996695792642603</v>
+      </c>
+      <c r="J71" s="11">
+        <v>8.8117647058823501</v>
+      </c>
+      <c r="K71" s="11">
+        <v>46.8125</v>
+      </c>
+      <c r="L71" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="17.5">
+      <c r="A72" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" s="8">
+        <v>45209</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D72" s="7">
+        <v>10664</v>
+      </c>
+      <c r="E72" s="7">
+        <v>185</v>
+      </c>
+      <c r="F72" s="9">
+        <v>820</v>
+      </c>
+      <c r="G72" s="9">
+        <v>840</v>
+      </c>
+      <c r="H72" s="9">
+        <v>20</v>
+      </c>
+      <c r="I72" s="10">
+        <v>0.78302371686614303</v>
+      </c>
+      <c r="J72" s="11">
+        <v>12.6952380952381</v>
+      </c>
+      <c r="K72" s="11">
+        <v>57.643243243243198</v>
+      </c>
+      <c r="L72" s="12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="17.5">
+      <c r="A73" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B73" s="8">
+        <v>42831</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="7">
+        <v>10152</v>
+      </c>
+      <c r="E73" s="7">
+        <v>250</v>
+      </c>
+      <c r="F73" s="9">
+        <v>850</v>
+      </c>
+      <c r="G73" s="9">
+        <v>812</v>
+      </c>
+      <c r="H73" s="9">
+        <v>-38</v>
+      </c>
+      <c r="I73" s="10">
+        <v>0.74542917982230705</v>
+      </c>
+      <c r="J73" s="11">
+        <v>12.502463054187199</v>
+      </c>
+      <c r="K73" s="11">
+        <v>40.607999999999997</v>
+      </c>
+      <c r="L73" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="17.5">
+      <c r="A74" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="B74" s="8">
+        <v>42795</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D74" s="7">
+        <v>9875</v>
+      </c>
+      <c r="E74" s="7">
+        <v>250</v>
+      </c>
+      <c r="F74" s="9">
+        <v>830</v>
+      </c>
+      <c r="G74" s="9">
+        <v>800</v>
+      </c>
+      <c r="H74" s="9">
+        <v>-30</v>
+      </c>
+      <c r="I74" s="10">
+        <v>0.72508994786695102</v>
+      </c>
+      <c r="J74" s="11">
+        <v>12.34375</v>
+      </c>
+      <c r="K74" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="L74" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="17.5">
+      <c r="A75" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" s="8">
+        <v>43767</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D75" s="7">
+        <v>5978</v>
+      </c>
+      <c r="E75" s="7">
+        <v>125</v>
+      </c>
+      <c r="F75" s="9">
+        <v>750</v>
+      </c>
+      <c r="G75" s="9">
+        <v>749</v>
+      </c>
+      <c r="H75" s="9">
+        <v>-1</v>
+      </c>
+      <c r="I75" s="10">
+        <v>0.43894559071884898</v>
+      </c>
+      <c r="J75" s="11">
+        <v>7.9813084112149504</v>
+      </c>
+      <c r="K75" s="11">
+        <v>47.823999999999998</v>
+      </c>
+      <c r="L75" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="17.5">
+      <c r="A76" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B76" s="8">
+        <v>43474</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D76" s="7">
+        <v>9292</v>
+      </c>
+      <c r="E76" s="7">
+        <v>300</v>
+      </c>
+      <c r="F76" s="9">
+        <v>800</v>
+      </c>
+      <c r="G76" s="9">
+        <v>730</v>
+      </c>
+      <c r="H76" s="9">
+        <v>-70</v>
+      </c>
+      <c r="I76" s="10">
+        <v>0.68228210588148896</v>
+      </c>
+      <c r="J76" s="11">
+        <v>12.7287671232877</v>
+      </c>
+      <c r="K76" s="11">
+        <v>30.973333333333301</v>
+      </c>
+      <c r="L76" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="17.5">
+      <c r="A77" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" s="8">
+        <v>42572</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="7">
+        <v>9560</v>
+      </c>
+      <c r="E77" s="7">
+        <v>250</v>
+      </c>
+      <c r="F77" s="9">
+        <v>780</v>
+      </c>
+      <c r="G77" s="9">
+        <v>730</v>
+      </c>
+      <c r="H77" s="9">
+        <v>-50</v>
+      </c>
+      <c r="I77" s="10">
+        <v>0.70196049636537206</v>
+      </c>
+      <c r="J77" s="11">
+        <v>13.0958904109589</v>
+      </c>
+      <c r="K77" s="11">
+        <v>38.24</v>
+      </c>
+      <c r="L77" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="17.5">
+      <c r="A78" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B78" s="8">
+        <v>43518</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78" s="7">
+        <v>6261</v>
+      </c>
+      <c r="E78" s="7">
+        <v>120</v>
+      </c>
+      <c r="F78" s="9">
+        <v>740</v>
+      </c>
+      <c r="G78" s="9">
+        <v>720</v>
+      </c>
+      <c r="H78" s="9">
+        <v>-20</v>
+      </c>
+      <c r="I78" s="10">
+        <v>0.459725383655188</v>
+      </c>
+      <c r="J78" s="11">
+        <v>8.6958333333333293</v>
+      </c>
+      <c r="K78" s="11">
+        <v>52.174999999999997</v>
+      </c>
+      <c r="L78" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="17.5">
+      <c r="A79" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B79" s="8">
+        <v>43653</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D79" s="7">
+        <v>9489</v>
+      </c>
+      <c r="E79" s="7">
+        <v>225</v>
+      </c>
+      <c r="F79" s="9">
+        <v>710</v>
+      </c>
+      <c r="G79" s="9">
+        <v>720</v>
+      </c>
+      <c r="H79" s="9">
+        <v>10</v>
+      </c>
+      <c r="I79" s="10">
+        <v>0.69674719142374597</v>
+      </c>
+      <c r="J79" s="11">
+        <v>13.179166666666699</v>
+      </c>
+      <c r="K79" s="11">
+        <v>42.173333333333296</v>
+      </c>
+      <c r="L79" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="17.5">
+      <c r="A80" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B80" s="15">
+        <v>43538</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D80" s="14">
+        <v>5414</v>
+      </c>
+      <c r="E80" s="14">
+        <v>120</v>
+      </c>
+      <c r="F80" s="16">
+        <v>710</v>
+      </c>
+      <c r="G80" s="16">
+        <v>690</v>
+      </c>
+      <c r="H80" s="16">
+        <v>-20</v>
+      </c>
+      <c r="I80" s="17">
+        <v>0.397532858506498</v>
+      </c>
+      <c r="J80" s="18">
+        <v>7.8463768115942001</v>
+      </c>
+      <c r="K80" s="18">
+        <v>45.116666666666703</v>
+      </c>
+      <c r="L80" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="17.5">
+      <c r="A81" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B81" s="15">
+        <v>43503</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D81" s="14">
+        <v>8902</v>
+      </c>
+      <c r="E81" s="14">
+        <v>200</v>
+      </c>
+      <c r="F81" s="16">
+        <v>628</v>
+      </c>
+      <c r="G81" s="16">
+        <v>674</v>
+      </c>
+      <c r="H81" s="16">
+        <v>46</v>
+      </c>
+      <c r="I81" s="17">
+        <v>0.65364564211762999</v>
+      </c>
+      <c r="J81" s="18">
+        <v>13.207715133531201</v>
+      </c>
+      <c r="K81" s="18">
+        <v>44.51</v>
+      </c>
+      <c r="L81" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="17.5">
+      <c r="A82" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B82" s="15">
+        <v>43653</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D82" s="14">
+        <v>8500</v>
+      </c>
+      <c r="E82" s="14">
+        <v>180</v>
+      </c>
+      <c r="F82" s="16">
+        <v>668</v>
+      </c>
+      <c r="G82" s="16">
+        <v>666</v>
+      </c>
+      <c r="H82" s="16">
+        <v>-2</v>
+      </c>
+      <c r="I82" s="17">
+        <v>0.62412805639180602</v>
+      </c>
+      <c r="J82" s="18">
+        <v>12.762762762762801</v>
+      </c>
+      <c r="K82" s="18">
+        <v>47.2222222222222</v>
+      </c>
+      <c r="L82" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="17.5">
+      <c r="A83" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83" s="15">
+        <v>42496</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D83" s="14">
+        <v>7533</v>
+      </c>
+      <c r="E83" s="14">
+        <v>180</v>
+      </c>
+      <c r="F83" s="16">
+        <v>670</v>
+      </c>
+      <c r="G83" s="16">
+        <v>650</v>
+      </c>
+      <c r="H83" s="16">
+        <v>-20</v>
+      </c>
+      <c r="I83" s="17">
+        <v>0.55312431162346698</v>
+      </c>
+      <c r="J83" s="18">
+        <v>11.589230769230801</v>
+      </c>
+      <c r="K83" s="18">
+        <v>41.85</v>
+      </c>
+      <c r="L83" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="17.5">
+      <c r="A84" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B84" s="15">
+        <v>43034</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D84" s="14">
+        <v>6809</v>
+      </c>
+      <c r="E84" s="14">
+        <v>180</v>
+      </c>
+      <c r="F84" s="16">
+        <v>650</v>
+      </c>
+      <c r="G84" s="16">
+        <v>650</v>
+      </c>
+      <c r="H84" s="16">
+        <v>0</v>
+      </c>
+      <c r="I84" s="17">
+        <v>0.49996328658491801</v>
+      </c>
+      <c r="J84" s="18">
+        <v>10.4753846153846</v>
+      </c>
+      <c r="K84" s="18">
+        <v>37.827777777777797</v>
+      </c>
+      <c r="L84" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="17.5">
+      <c r="A85" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="B85" s="15">
+        <v>42496</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D85" s="14">
+        <v>6069</v>
+      </c>
+      <c r="E85" s="14">
+        <v>150</v>
+      </c>
+      <c r="F85" s="16">
+        <v>600</v>
+      </c>
+      <c r="G85" s="16">
+        <v>608</v>
+      </c>
+      <c r="H85" s="16">
+        <v>8</v>
+      </c>
+      <c r="I85" s="17">
+        <v>0.44562743226374901</v>
+      </c>
+      <c r="J85" s="18">
+        <v>9.9819078947368407</v>
+      </c>
+      <c r="K85" s="18">
+        <v>40.46</v>
+      </c>
+      <c r="L85" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="17.5">
+      <c r="A86" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B86" s="15">
+        <v>43669</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" s="14">
+        <v>4670</v>
+      </c>
+      <c r="E86" s="14">
+        <v>100</v>
+      </c>
+      <c r="F86" s="16">
+        <v>627</v>
+      </c>
+      <c r="G86" s="16">
+        <v>600</v>
+      </c>
+      <c r="H86" s="16">
+        <v>-27</v>
+      </c>
+      <c r="I86" s="17">
+        <v>0.34290329686467402</v>
+      </c>
+      <c r="J86" s="18">
+        <v>7.7833333333333297</v>
+      </c>
+      <c r="K86" s="18">
+        <v>46.7</v>
+      </c>
+      <c r="L86" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="17.5">
+      <c r="A87" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B87" s="15">
+        <v>43851</v>
+      </c>
+      <c r="C87" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D87" s="14">
+        <v>7711</v>
+      </c>
+      <c r="E87" s="14">
+        <v>150</v>
+      </c>
+      <c r="F87" s="16">
+        <v>607</v>
+      </c>
+      <c r="G87" s="16">
+        <v>600</v>
+      </c>
+      <c r="H87" s="16">
+        <v>-7</v>
+      </c>
+      <c r="I87" s="17">
+        <v>0.56619428739261302</v>
+      </c>
+      <c r="J87" s="18">
+        <v>12.8516666666667</v>
+      </c>
+      <c r="K87" s="18">
+        <v>51.406666666666702</v>
+      </c>
+      <c r="L87" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="17.5">
+      <c r="A88" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B88" s="15">
+        <v>44727</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D88" s="14">
+        <v>4312</v>
+      </c>
+      <c r="E88" s="14">
+        <v>92</v>
+      </c>
+      <c r="F88" s="16">
+        <v>568</v>
+      </c>
+      <c r="G88" s="16">
+        <v>588</v>
+      </c>
+      <c r="H88" s="16">
+        <v>20</v>
+      </c>
+      <c r="I88" s="17">
+        <v>0.31661649166605499</v>
+      </c>
+      <c r="J88" s="18">
+        <v>7.3333333333333304</v>
+      </c>
+      <c r="K88" s="18">
+        <v>46.869565217391298</v>
+      </c>
+      <c r="L88" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="17.5">
+      <c r="A89" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B89" s="15">
+        <v>44580</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D89" s="14">
+        <v>3579</v>
+      </c>
+      <c r="E89" s="14">
+        <v>53</v>
+      </c>
+      <c r="F89" s="16">
+        <v>580</v>
+      </c>
+      <c r="G89" s="16">
+        <v>580</v>
+      </c>
+      <c r="H89" s="16">
+        <v>0</v>
+      </c>
+      <c r="I89" s="17">
+        <v>0.26279462515603202</v>
+      </c>
+      <c r="J89" s="18">
+        <v>6.17068965517241</v>
+      </c>
+      <c r="K89" s="18">
+        <v>67.528301886792406</v>
+      </c>
+      <c r="L89" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="17.5">
+      <c r="A90" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B90" s="15">
+        <v>42558</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D90" s="14">
+        <v>4202</v>
+      </c>
+      <c r="E90" s="14">
+        <v>120</v>
+      </c>
+      <c r="F90" s="16">
+        <v>590</v>
+      </c>
+      <c r="G90" s="16">
+        <v>579</v>
+      </c>
+      <c r="H90" s="16">
+        <v>-11</v>
+      </c>
+      <c r="I90" s="17">
+        <v>0.30853954034804298</v>
+      </c>
+      <c r="J90" s="18">
+        <v>7.2573402417962001</v>
+      </c>
+      <c r="K90" s="18">
+        <v>35.016666666666701</v>
+      </c>
+      <c r="L90" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="17.5">
+      <c r="A91" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B91" s="15">
+        <v>44580</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" s="14">
+        <v>4923</v>
+      </c>
+      <c r="E91" s="14">
+        <v>107</v>
+      </c>
+      <c r="F91" s="16">
+        <v>560</v>
+      </c>
+      <c r="G91" s="16">
+        <v>550</v>
+      </c>
+      <c r="H91" s="16">
+        <v>-10</v>
+      </c>
+      <c r="I91" s="17">
+        <v>0.36148028489610101</v>
+      </c>
+      <c r="J91" s="18">
+        <v>8.9509090909090894</v>
+      </c>
+      <c r="K91" s="18">
+        <v>46.009345794392502</v>
+      </c>
+      <c r="L91" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="17.5">
+      <c r="A92" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" s="15">
+        <v>42080</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" s="14">
+        <v>5227</v>
+      </c>
+      <c r="E92" s="14">
+        <v>250</v>
+      </c>
+      <c r="F92" s="16">
+        <v>548</v>
+      </c>
+      <c r="G92" s="16">
+        <v>550</v>
+      </c>
+      <c r="H92" s="16">
+        <v>2</v>
+      </c>
+      <c r="I92" s="17">
+        <v>0.38380204126587902</v>
+      </c>
+      <c r="J92" s="18">
+        <v>9.5036363636363603</v>
+      </c>
+      <c r="K92" s="18">
+        <v>20.908000000000001</v>
+      </c>
+      <c r="L92" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="17.5">
+      <c r="A93" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B93" s="15">
+        <v>43578</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" s="14">
+        <v>3598</v>
+      </c>
+      <c r="E93" s="14">
+        <v>75</v>
+      </c>
+      <c r="F93" s="16">
+        <v>590</v>
+      </c>
+      <c r="G93" s="16">
+        <v>548</v>
+      </c>
+      <c r="H93" s="16">
+        <v>-42</v>
+      </c>
+      <c r="I93" s="17">
+        <v>0.26418973492914299</v>
+      </c>
+      <c r="J93" s="18">
+        <v>6.5656934306569301</v>
+      </c>
+      <c r="K93" s="18">
+        <v>47.973333333333301</v>
+      </c>
+      <c r="L93" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="17.5">
+      <c r="A94" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B94" s="15">
+        <v>43811</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D94" s="14">
+        <v>4888</v>
+      </c>
+      <c r="E94" s="14">
+        <v>130</v>
+      </c>
+      <c r="F94" s="16">
+        <v>505</v>
+      </c>
+      <c r="G94" s="16">
+        <v>505</v>
+      </c>
+      <c r="H94" s="16">
+        <v>0</v>
+      </c>
+      <c r="I94" s="17">
+        <v>0.35891034584037002</v>
+      </c>
+      <c r="J94" s="18">
+        <v>9.6792079207920807</v>
+      </c>
+      <c r="K94" s="18">
+        <v>37.6</v>
+      </c>
+      <c r="L94" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="17.5">
+      <c r="A95" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B95" s="23">
+        <v>42975</v>
+      </c>
+      <c r="C95" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D95" s="24">
+        <v>7515</v>
+      </c>
+      <c r="E95" s="24">
+        <v>195</v>
+      </c>
+      <c r="F95" s="25">
+        <v>500</v>
+      </c>
+      <c r="G95" s="25">
+        <v>494</v>
+      </c>
+      <c r="H95" s="25">
+        <v>-6</v>
+      </c>
+      <c r="I95" s="26">
+        <v>0.55180262868051999</v>
+      </c>
+      <c r="J95" s="27">
+        <v>15.212550607287399</v>
+      </c>
+      <c r="K95" s="27">
+        <v>38.538461538461497</v>
+      </c>
+      <c r="L95" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="17.5">
+      <c r="A96" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B96" s="23">
+        <v>43070</v>
+      </c>
+      <c r="C96" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D96" s="24">
+        <v>3904</v>
+      </c>
+      <c r="E96" s="24">
+        <v>120</v>
+      </c>
+      <c r="F96" s="25">
+        <v>499</v>
+      </c>
+      <c r="G96" s="25">
+        <v>480</v>
+      </c>
+      <c r="H96" s="25">
+        <v>-19</v>
+      </c>
+      <c r="I96" s="26">
+        <v>0.28665834495924802</v>
+      </c>
+      <c r="J96" s="27">
+        <v>8.1333333333333293</v>
+      </c>
+      <c r="K96" s="27">
+        <v>32.533333333333303</v>
+      </c>
+      <c r="L96" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="17.5">
+      <c r="A97" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="B97" s="23">
+        <v>42157</v>
+      </c>
+      <c r="C97" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D97" s="24">
+        <v>5758</v>
+      </c>
+      <c r="E97" s="24">
+        <v>250</v>
+      </c>
+      <c r="F97" s="25">
+        <v>500</v>
+      </c>
+      <c r="G97" s="25">
+        <v>469</v>
+      </c>
+      <c r="H97" s="25">
+        <v>-31</v>
+      </c>
+      <c r="I97" s="26">
+        <v>0.42279168808282502</v>
+      </c>
+      <c r="J97" s="27">
+        <v>12.2771855010661</v>
+      </c>
+      <c r="K97" s="27">
+        <v>23.032</v>
+      </c>
+      <c r="L97" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="17.5">
+      <c r="A98" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B98" s="23">
+        <v>42961</v>
+      </c>
+      <c r="C98" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D98" s="24">
+        <v>6874</v>
+      </c>
+      <c r="E98" s="24">
+        <v>210</v>
+      </c>
+      <c r="F98" s="25">
+        <v>452</v>
+      </c>
+      <c r="G98" s="25">
+        <v>430</v>
+      </c>
+      <c r="H98" s="25">
+        <v>-22</v>
+      </c>
+      <c r="I98" s="26">
+        <v>0.50473603054556104</v>
+      </c>
+      <c r="J98" s="27">
+        <v>15.986046511627899</v>
+      </c>
+      <c r="K98" s="27">
+        <v>32.733333333333299</v>
+      </c>
+      <c r="L98" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="17.5">
+      <c r="A99" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B99" s="23">
+        <v>44543</v>
+      </c>
+      <c r="C99" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D99" s="24">
+        <v>8999</v>
+      </c>
+      <c r="E99" s="24">
+        <v>135</v>
+      </c>
+      <c r="F99" s="25">
+        <v>411</v>
+      </c>
+      <c r="G99" s="25">
+        <v>429</v>
+      </c>
+      <c r="H99" s="25">
+        <v>18</v>
+      </c>
+      <c r="I99" s="26">
+        <v>0.66076804464351302</v>
+      </c>
+      <c r="J99" s="27">
+        <v>20.97668997669</v>
+      </c>
+      <c r="K99" s="27">
+        <v>66.659259259259301</v>
+      </c>
+      <c r="L99" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="17.5">
+      <c r="A100" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B100" s="23">
+        <v>42668</v>
+      </c>
+      <c r="C100" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" s="24">
+        <v>2338</v>
+      </c>
+      <c r="E100" s="24">
+        <v>75</v>
+      </c>
+      <c r="F100" s="25">
+        <v>447</v>
+      </c>
+      <c r="G100" s="25">
+        <v>420</v>
+      </c>
+      <c r="H100" s="25">
+        <v>-27</v>
+      </c>
+      <c r="I100" s="26">
+        <v>0.17167192892282801</v>
+      </c>
+      <c r="J100" s="27">
+        <v>5.56666666666667</v>
+      </c>
+      <c r="K100" s="27">
+        <v>31.1733333333333</v>
+      </c>
+      <c r="L100" s="28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="17.5">
+      <c r="A101" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B101" s="23">
+        <v>43419</v>
+      </c>
+      <c r="C101" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D101" s="24">
+        <v>4764</v>
+      </c>
+      <c r="E101" s="24">
+        <v>225</v>
+      </c>
+      <c r="F101" s="25">
+        <v>420</v>
+      </c>
+      <c r="G101" s="25">
+        <v>401</v>
+      </c>
+      <c r="H101" s="25">
+        <v>-19</v>
+      </c>
+      <c r="I101" s="26">
+        <v>0.349805418900066</v>
+      </c>
+      <c r="J101" s="27">
+        <v>11.8802992518703</v>
+      </c>
+      <c r="K101" s="27">
+        <v>21.1733333333333</v>
+      </c>
+      <c r="L101" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="17.5">
+      <c r="A102" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B102" s="23">
+        <v>42843</v>
+      </c>
+      <c r="C102" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D102" s="24">
+        <v>4360</v>
+      </c>
+      <c r="E102" s="24">
+        <v>185</v>
+      </c>
+      <c r="F102" s="25">
+        <v>410</v>
+      </c>
+      <c r="G102" s="25">
+        <v>400</v>
+      </c>
+      <c r="H102" s="25">
+        <v>-10</v>
+      </c>
+      <c r="I102" s="26">
+        <v>0.32014097951391401</v>
+      </c>
+      <c r="J102" s="27">
+        <v>10.9</v>
+      </c>
+      <c r="K102" s="27">
+        <v>23.5675675675676</v>
+      </c>
+      <c r="L102" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="17.5">
+      <c r="A103" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B103" s="23">
+        <v>43899</v>
+      </c>
+      <c r="C103" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D103" s="24">
+        <v>4432</v>
+      </c>
+      <c r="E103" s="24">
+        <v>190</v>
+      </c>
+      <c r="F103" s="25">
+        <v>399</v>
+      </c>
+      <c r="G103" s="25">
+        <v>400</v>
+      </c>
+      <c r="H103" s="25">
+        <v>1</v>
+      </c>
+      <c r="I103" s="26">
+        <v>0.32542771128570402</v>
+      </c>
+      <c r="J103" s="27">
+        <v>11.08</v>
+      </c>
+      <c r="K103" s="27">
+        <v>23.3263157894737</v>
+      </c>
+      <c r="L103" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="17.5">
+      <c r="A104" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="B104" s="23">
+        <v>42600</v>
+      </c>
+      <c r="C104" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D104" s="24">
+        <v>3843</v>
+      </c>
+      <c r="E104" s="24">
+        <v>115</v>
+      </c>
+      <c r="F104" s="25">
+        <v>380</v>
+      </c>
+      <c r="G104" s="25">
+        <v>390</v>
+      </c>
+      <c r="H104" s="25">
+        <v>10</v>
+      </c>
+      <c r="I104" s="26">
+        <v>0.28217930831926002</v>
+      </c>
+      <c r="J104" s="27">
+        <v>9.8538461538461508</v>
+      </c>
+      <c r="K104" s="27">
+        <v>33.417391304347802</v>
+      </c>
+      <c r="L104" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="17.5">
+      <c r="A105" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B105" s="23">
+        <v>42243</v>
+      </c>
+      <c r="C105" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D105" s="24">
+        <v>4606</v>
+      </c>
+      <c r="E105" s="24">
+        <v>225</v>
+      </c>
+      <c r="F105" s="25">
+        <v>430</v>
+      </c>
+      <c r="G105" s="25">
+        <v>380</v>
+      </c>
+      <c r="H105" s="25">
+        <v>-50</v>
+      </c>
+      <c r="I105" s="26">
+        <v>0.33820397973419503</v>
+      </c>
+      <c r="J105" s="27">
+        <v>12.1210526315789</v>
+      </c>
+      <c r="K105" s="27">
+        <v>20.471111111111099</v>
+      </c>
+      <c r="L105" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="17.5">
+      <c r="A106" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B106" s="23">
+        <v>42522</v>
+      </c>
+      <c r="C106" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D106" s="24">
+        <v>4162</v>
+      </c>
+      <c r="E106" s="24">
+        <v>150</v>
+      </c>
+      <c r="F106" s="25">
+        <v>400</v>
+      </c>
+      <c r="G106" s="25">
+        <v>380</v>
+      </c>
+      <c r="H106" s="25">
+        <v>-20</v>
+      </c>
+      <c r="I106" s="26">
+        <v>0.30560246714149403</v>
+      </c>
+      <c r="J106" s="27">
+        <v>10.9526315789474</v>
+      </c>
+      <c r="K106" s="27">
+        <v>27.746666666666702</v>
+      </c>
+      <c r="L106" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="17.5">
+      <c r="A107" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B107" s="23">
+        <v>44245</v>
+      </c>
+      <c r="C107" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D107" s="24">
+        <v>8105</v>
+      </c>
+      <c r="E107" s="24">
+        <v>185</v>
+      </c>
+      <c r="F107" s="25">
+        <v>370</v>
+      </c>
+      <c r="G107" s="25">
+        <v>380</v>
+      </c>
+      <c r="H107" s="25">
+        <v>10</v>
+      </c>
+      <c r="I107" s="26">
+        <v>0.59512445847712803</v>
+      </c>
+      <c r="J107" s="27">
+        <v>21.328947368421101</v>
+      </c>
+      <c r="K107" s="27">
+        <v>43.8108108108108</v>
+      </c>
+      <c r="L107" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="17.5">
+      <c r="A108" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B108" s="23">
+        <v>43405</v>
+      </c>
+      <c r="C108" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D108" s="24">
+        <v>3790</v>
+      </c>
+      <c r="E108" s="24">
+        <v>150</v>
+      </c>
+      <c r="F108" s="25">
+        <v>380</v>
+      </c>
+      <c r="G108" s="25">
+        <v>370</v>
+      </c>
+      <c r="H108" s="25">
+        <v>-10</v>
+      </c>
+      <c r="I108" s="26">
+        <v>0.27828768632058198</v>
+      </c>
+      <c r="J108" s="27">
+        <v>10.243243243243199</v>
+      </c>
+      <c r="K108" s="27">
+        <v>25.266666666666701</v>
+      </c>
+      <c r="L108" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="17.5">
+      <c r="A109" s="53" t="s">
+        <v>137</v>
+      </c>
+      <c r="B109" s="23">
+        <v>41901</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109" s="24">
+        <v>4332</v>
+      </c>
+      <c r="E109" s="24">
+        <v>170</v>
+      </c>
+      <c r="F109" s="25">
+        <v>377</v>
+      </c>
+      <c r="G109" s="25">
+        <v>357</v>
+      </c>
+      <c r="H109" s="25">
+        <v>-20</v>
+      </c>
+      <c r="I109" s="26">
+        <v>0.31808502826932999</v>
+      </c>
+      <c r="J109" s="27">
+        <v>12.134453781512599</v>
+      </c>
+      <c r="K109" s="27">
+        <v>25.482352941176501</v>
+      </c>
+      <c r="L109" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="17.5">
+      <c r="A110" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B110" s="23">
+        <v>42843</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" s="24">
+        <v>3863</v>
+      </c>
+      <c r="E110" s="24">
+        <v>150</v>
+      </c>
+      <c r="F110" s="25">
+        <v>380</v>
+      </c>
+      <c r="G110" s="25">
+        <v>350</v>
+      </c>
+      <c r="H110" s="25">
+        <v>-30</v>
+      </c>
+      <c r="I110" s="26">
+        <v>0.28364784492253498</v>
+      </c>
+      <c r="J110" s="27">
+        <v>11.0371428571429</v>
+      </c>
+      <c r="K110" s="27">
+        <v>25.753333333333298</v>
+      </c>
+      <c r="L110" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="17.5">
+      <c r="A111" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B111" s="23">
+        <v>42586</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D111" s="24">
+        <v>3700</v>
+      </c>
+      <c r="E111" s="24">
+        <v>120</v>
+      </c>
+      <c r="F111" s="25">
+        <v>360</v>
+      </c>
+      <c r="G111" s="25">
+        <v>350</v>
+      </c>
+      <c r="H111" s="25">
+        <v>-10</v>
+      </c>
+      <c r="I111" s="26">
+        <v>0.27167927160584499</v>
+      </c>
+      <c r="J111" s="27">
+        <v>10.5714285714286</v>
+      </c>
+      <c r="K111" s="27">
+        <v>30.8333333333333</v>
+      </c>
+      <c r="L111" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="17.5">
+      <c r="A112" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="B112" s="23">
+        <v>41904</v>
+      </c>
+      <c r="C112" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D112" s="24">
+        <v>3623</v>
+      </c>
+      <c r="E112" s="24">
+        <v>165</v>
+      </c>
+      <c r="F112" s="25">
+        <v>320</v>
+      </c>
+      <c r="G112" s="25">
+        <v>325</v>
+      </c>
+      <c r="H112" s="25">
+        <v>5</v>
+      </c>
+      <c r="I112" s="26">
+        <v>0.26602540568323702</v>
+      </c>
+      <c r="J112" s="27">
+        <v>11.147692307692299</v>
+      </c>
+      <c r="K112" s="27">
+        <v>21.9575757575758</v>
+      </c>
+      <c r="L112" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="17.5">
+      <c r="A113" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B113" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C113" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" s="24">
+        <v>2283</v>
+      </c>
+      <c r="E113" s="24">
+        <v>120</v>
+      </c>
+      <c r="F113" s="25">
+        <v>300</v>
+      </c>
+      <c r="G113" s="25">
+        <v>300</v>
+      </c>
+      <c r="H113" s="25">
+        <v>0</v>
+      </c>
+      <c r="I113" s="26">
+        <v>0.16763345326382301</v>
+      </c>
+      <c r="J113" s="27">
+        <v>7.61</v>
+      </c>
+      <c r="K113" s="27">
+        <v>19.024999999999999</v>
+      </c>
+      <c r="L113" s="28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="17.5">
+      <c r="A114" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="B114" s="31">
+        <v>42668</v>
+      </c>
+      <c r="C114" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="D114" s="32">
+        <v>1749</v>
+      </c>
+      <c r="E114" s="32">
+        <v>75</v>
+      </c>
+      <c r="F114" s="33">
+        <v>280</v>
+      </c>
+      <c r="G114" s="33">
+        <v>275</v>
+      </c>
+      <c r="H114" s="33">
+        <v>-5</v>
+      </c>
+      <c r="I114" s="34">
+        <v>0.12842352595638501</v>
+      </c>
+      <c r="J114" s="35">
+        <v>6.36</v>
+      </c>
+      <c r="K114" s="35">
+        <v>23.32</v>
+      </c>
+      <c r="L114" s="36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="17.5">
+      <c r="A115" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="B115" s="31">
+        <v>42843</v>
+      </c>
+      <c r="C115" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="D115" s="32">
+        <v>1199</v>
+      </c>
+      <c r="E115" s="32">
+        <v>50</v>
+      </c>
+      <c r="F115" s="33">
+        <v>256</v>
+      </c>
+      <c r="G115" s="33">
+        <v>256</v>
+      </c>
+      <c r="H115" s="33">
+        <v>0</v>
+      </c>
+      <c r="I115" s="34">
+        <v>8.80387693663265E-2</v>
+      </c>
+      <c r="J115" s="35">
+        <v>4.68359375</v>
+      </c>
+      <c r="K115" s="35">
+        <v>23.98</v>
+      </c>
+      <c r="L115" s="36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="17.5">
+      <c r="A116" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="B116" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C116" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="D116" s="32">
+        <v>1797</v>
+      </c>
+      <c r="E116" s="32">
+        <v>80</v>
+      </c>
+      <c r="F116" s="33">
+        <v>250</v>
+      </c>
+      <c r="G116" s="33">
+        <v>250</v>
+      </c>
+      <c r="H116" s="33">
+        <v>0</v>
+      </c>
+      <c r="I116" s="34">
+        <v>0.13194801380424401</v>
+      </c>
+      <c r="J116" s="35">
+        <v>7.1879999999999997</v>
+      </c>
+      <c r="K116" s="35">
+        <v>22.462499999999999</v>
+      </c>
+      <c r="L116" s="36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="17.5">
+      <c r="A117" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="B117" s="31">
+        <v>42590</v>
+      </c>
+      <c r="C117" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="D117" s="32">
+        <v>1724</v>
+      </c>
+      <c r="E117" s="32">
+        <v>75</v>
+      </c>
+      <c r="F117" s="33">
+        <v>250</v>
+      </c>
+      <c r="G117" s="33">
+        <v>240</v>
+      </c>
+      <c r="H117" s="33">
+        <v>-10</v>
+      </c>
+      <c r="I117" s="34">
+        <v>0.12658785520229099</v>
+      </c>
+      <c r="J117" s="35">
+        <v>7.18333333333333</v>
+      </c>
+      <c r="K117" s="35">
+        <v>22.9866666666667</v>
+      </c>
+      <c r="L117" s="36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="17.5">
+      <c r="A118" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="B118" s="31">
+        <v>42872</v>
+      </c>
+      <c r="C118" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="D118" s="32">
+        <v>1082</v>
+      </c>
+      <c r="E118" s="32">
+        <v>30</v>
+      </c>
+      <c r="F118" s="33">
+        <v>260</v>
+      </c>
+      <c r="G118" s="33">
+        <v>235</v>
+      </c>
+      <c r="H118" s="33">
+        <v>-25</v>
+      </c>
+      <c r="I118" s="34">
+        <v>7.9447830237168601E-2</v>
+      </c>
+      <c r="J118" s="35">
+        <v>4.6042553191489404</v>
+      </c>
+      <c r="K118" s="35">
+        <v>36.066666666666698</v>
+      </c>
+      <c r="L118" s="36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="17.5">
+      <c r="A119" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="B119" s="31">
+        <v>42236</v>
+      </c>
+      <c r="C119" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="D119" s="32">
+        <v>1750</v>
+      </c>
+      <c r="E119" s="32">
+        <v>90</v>
+      </c>
+      <c r="F119" s="33">
+        <v>210</v>
+      </c>
+      <c r="G119" s="33">
+        <v>220</v>
+      </c>
+      <c r="H119" s="33">
+        <v>10</v>
+      </c>
+      <c r="I119" s="34">
+        <v>0.12849695278654799</v>
+      </c>
+      <c r="J119" s="35">
+        <v>7.9545454545454497</v>
+      </c>
+      <c r="K119" s="35">
+        <v>19.4444444444444</v>
+      </c>
+      <c r="L119" s="36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="17.5">
+      <c r="A120" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="B120" s="31">
+        <v>44245</v>
+      </c>
+      <c r="C120" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D120" s="32">
+        <v>5922</v>
+      </c>
+      <c r="E120" s="32">
+        <v>125</v>
+      </c>
+      <c r="F120" s="33">
+        <v>222</v>
+      </c>
+      <c r="G120" s="33">
+        <v>219</v>
+      </c>
+      <c r="H120" s="33">
+        <v>-3</v>
+      </c>
+      <c r="I120" s="34">
+        <v>0.43483368822967899</v>
+      </c>
+      <c r="J120" s="35">
+        <v>27.041095890411</v>
+      </c>
+      <c r="K120" s="35">
+        <v>47.375999999999998</v>
+      </c>
+      <c r="L120" s="36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="17.5">
+      <c r="A121" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="B121" s="31">
+        <v>44209</v>
+      </c>
+      <c r="C121" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="D121" s="32">
+        <v>525</v>
+      </c>
+      <c r="E121" s="32">
+        <v>30</v>
+      </c>
+      <c r="F121" s="33">
+        <v>180</v>
+      </c>
+      <c r="G121" s="33">
+        <v>200</v>
+      </c>
+      <c r="H121" s="33">
+        <v>20</v>
+      </c>
+      <c r="I121" s="34">
+        <v>3.8549085835964503E-2</v>
+      </c>
+      <c r="J121" s="35">
+        <v>2.625</v>
+      </c>
+      <c r="K121" s="35">
+        <v>17.5</v>
+      </c>
+      <c r="L121" s="36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" ht="17.5">
+      <c r="A122" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B122" s="31">
+        <v>42905</v>
+      </c>
+      <c r="C122" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D122" s="32">
+        <v>4060</v>
+      </c>
+      <c r="E122" s="32">
+        <v>120</v>
+      </c>
+      <c r="F122" s="33">
+        <v>154</v>
+      </c>
+      <c r="G122" s="33">
+        <v>148</v>
+      </c>
+      <c r="H122" s="33">
+        <v>-6</v>
+      </c>
+      <c r="I122" s="34">
+        <v>0.29811293046479198</v>
+      </c>
+      <c r="J122" s="35">
+        <v>27.4324324324324</v>
+      </c>
+      <c r="K122" s="35">
+        <v>33.8333333333333</v>
+      </c>
+      <c r="L122" s="36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>